--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_ListFromRange/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_ListFromRange/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4b67654abc7d457d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra3c5681911004564"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_ListFromRange/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_ListFromRange/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra3c5681911004564"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R66b8977c56e84b54"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_ListFromRange/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_ListFromRange/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R66b8977c56e84b54"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R85c4fa3c523c48fc"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_ListFromRange/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_ListFromRange/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R85c4fa3c523c48fc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3f74a18cd60541c6"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_ListFromRange/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_ListFromRange/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3f74a18cd60541c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R94aec12a3bc34dee"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_ListFromRange/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_ListFromRange/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R94aec12a3bc34dee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra867e9731b334569"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_ListFromRange/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_ListFromRange/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra867e9731b334569"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R695a5a681700411c"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_ListFromRange/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_ListFromRange/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R695a5a681700411c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4246226f04ef43b0"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_ListFromRange/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_ListFromRange/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4246226f04ef43b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R73f7be80dac548c7"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_ListFromRange/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_ListFromRange/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R73f7be80dac548c7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7df1dd3446f944d5"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_ListFromRange/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_ListFromRange/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7df1dd3446f944d5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re3c24717edbc4d6e"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_ListFromRange/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_ListFromRange/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re3c24717edbc4d6e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra3e65b40faae47dd"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_ListFromRange/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_ListFromRange/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra3e65b40faae47dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rcc68114323ae43ce"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_ListFromRange/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_ListFromRange/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rcc68114323ae43ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2440bda1ac0f4845"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_ListFromRange/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_ListFromRange/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2440bda1ac0f4845"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1d06e0666a6f46b8"/>
   </x:sheets>
 </x:workbook>
 </file>
